--- a/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_INVEREADY GIPUZKOA.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_INVEREADY GIPUZKOA.xlsx
@@ -565,13 +565,13 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>10.7253</v>
+        <v>6.551699999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8527</v>
+        <v>3.6471</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8726</v>
+        <v>2.9047</v>
       </c>
       <c r="G2" t="n">
         <v>3.5649</v>
@@ -610,13 +610,13 @@
         <v>5.7272</v>
       </c>
       <c r="S2" t="n">
-        <v>7.2803</v>
+        <v>3.1069</v>
       </c>
       <c r="T2" t="n">
-        <v>5.1767</v>
+        <v>1.9711</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1036</v>
+        <v>1.1356</v>
       </c>
       <c r="V2" t="n">
         <v>1.8624</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>O. HANZLIK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3.432</v>
+        <v>3.3372</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3863</v>
+        <v>4.4454</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0457</v>
+        <v>-1.1082</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.1152</v>
+        <v>-2.0937</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.3488</v>
+        <v>-2.7623</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.7665</v>
+        <v>0.6686000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.6565</v>
+        <v>3.2294</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.6132</v>
+        <v>1.0371</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.04330000000000001</v>
+        <v>2.1924</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.4588</v>
+        <v>-5.323</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7356</v>
+        <v>-3.7993</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.7232</v>
+        <v>-1.5237</v>
       </c>
       <c r="P3" t="n">
-        <v>4.6258</v>
+        <v>3.7446</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.3041</v>
       </c>
       <c r="R3" t="n">
-        <v>4.6258</v>
+        <v>7.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4087</v>
+        <v>2.2421</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6726</v>
+        <v>1.7228</v>
       </c>
       <c r="U3" t="n">
-        <v>0.736</v>
+        <v>0.5192</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.4873</v>
+        <v>-0.5559000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>0.37</v>
+        <v>2.7973</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8572</v>
+        <v>-3.3532</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. HANZLIK</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3.303900000000001</v>
+        <v>2.3243</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4985</v>
+        <v>0.2786</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1947</v>
+        <v>2.0457</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.0937</v>
+        <v>-4.1152</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.7623</v>
+        <v>-2.3488</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6686000000000001</v>
+        <v>-1.7665</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2294</v>
+        <v>-1.6565</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0371</v>
+        <v>-1.6132</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1924</v>
+        <v>-0.04330000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.323</v>
+        <v>-2.4588</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.7993</v>
+        <v>-0.7356</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5237</v>
+        <v>-1.7232</v>
       </c>
       <c r="P4" t="n">
-        <v>3.7446</v>
+        <v>4.6258</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.3041</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>7.0487</v>
+        <v>4.6258</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2088</v>
+        <v>2.301</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7759</v>
+        <v>1.5651</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4328</v>
+        <v>0.736</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5559000000000001</v>
+        <v>-0.4873</v>
       </c>
       <c r="W4" t="n">
-        <v>2.7973</v>
+        <v>0.37</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.3532</v>
+        <v>-0.8572</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5120999999999999</v>
+        <v>0.6832999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0608</v>
+        <v>4.9436</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.5486</v>
+        <v>-4.2603</v>
       </c>
       <c r="G5" t="n">
         <v>-3.4452</v>
@@ -844,13 +844,13 @@
         <v>3.3042</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1968</v>
+        <v>0.3679</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4013</v>
+        <v>0.2842</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2046</v>
+        <v>0.08360000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0.4565</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1914</v>
+        <v>-0.8273000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4433000000000007</v>
+        <v>2.5063</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7482</v>
+        <v>-3.3338</v>
       </c>
       <c r="G6" t="n">
-        <v>-9.2814</v>
+        <v>2.0613</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7887</v>
+        <v>2.1815</v>
       </c>
       <c r="I6" t="n">
-        <v>-7.4927</v>
+        <v>-0.1201</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01820000000000022</v>
+        <v>7.903600000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8387</v>
+        <v>4.0896</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.8205</v>
+        <v>3.8141</v>
       </c>
       <c r="M6" t="n">
-        <v>-9.2996</v>
+        <v>-5.8422</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.6274</v>
+        <v>-1.908</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.6721</v>
+        <v>-3.9343</v>
       </c>
       <c r="P6" t="n">
-        <v>5.2866</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1014</v>
+        <v>-5.5069</v>
       </c>
       <c r="R6" t="n">
-        <v>6.3879</v>
+        <v>4.846</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1206</v>
+        <v>-1.1864</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2699</v>
+        <v>-1.0094</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8506</v>
+        <v>-0.1772</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6829</v>
+        <v>-1.0413</v>
       </c>
       <c r="W6" t="n">
-        <v>0.37</v>
+        <v>1.1189</v>
       </c>
       <c r="X6" t="n">
-        <v>1.3129</v>
+        <v>-2.1602</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>A. ZUBIZARRETA ARANBARRI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0407</v>
+        <v>-1.5958</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6222</v>
+        <v>-2.7186</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.6628</v>
+        <v>1.1228</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0613</v>
+        <v>-1.8942</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1815</v>
+        <v>-3.4617</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1201</v>
+        <v>1.5674</v>
       </c>
       <c r="J7" t="n">
-        <v>7.903600000000001</v>
+        <v>-1.341</v>
       </c>
       <c r="K7" t="n">
-        <v>4.0896</v>
+        <v>-2.0625</v>
       </c>
       <c r="L7" t="n">
-        <v>3.8141</v>
+        <v>0.7215</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.8422</v>
+        <v>-0.5532</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.908</v>
+        <v>-1.3992</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.9343</v>
+        <v>0.846</v>
       </c>
       <c r="P7" t="n">
         <v>-0.6608000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.5069</v>
+        <v>-2.2028</v>
       </c>
       <c r="R7" t="n">
-        <v>4.846</v>
+        <v>1.5419</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.3999</v>
+        <v>0.0262</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.8935</v>
+        <v>-0.2938</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5063</v>
+        <v>0.32</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0413</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="W7" t="n">
         <v>1.1189</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1602</v>
+        <v>-0.1859</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ZUBIZARRETA ARANBARRI</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7376</v>
+        <v>-1.9773</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.4857</v>
+        <v>-0.5493999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.748</v>
+        <v>-1.4279</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8942</v>
+        <v>-9.2814</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.4617</v>
+        <v>-1.7887</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5674</v>
+        <v>-7.4927</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.341</v>
+        <v>0.01820000000000022</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.0625</v>
+        <v>2.8387</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7215</v>
+        <v>-2.8205</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5532</v>
+        <v>-9.2996</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3992</v>
+        <v>-4.6274</v>
       </c>
       <c r="O8" t="n">
-        <v>0.846</v>
+        <v>-4.6721</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6608000000000001</v>
+        <v>5.2866</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2028</v>
+        <v>-1.1014</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5419</v>
+        <v>6.3879</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1156</v>
+        <v>0.3347</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0609</v>
+        <v>0.1636</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.05480000000000002</v>
+        <v>0.1708999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.6829</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1189</v>
+        <v>0.37</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1859</v>
+        <v>1.3129</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7787</v>
+        <v>-3.2786</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.09400000000000003</v>
+        <v>0.2043999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.6847</v>
+        <v>-3.4829</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4256</v>
@@ -1156,13 +1156,13 @@
         <v>1.5419</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5074</v>
+        <v>-1.0072</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6125</v>
+        <v>-0.3141</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8949</v>
+        <v>-0.6932</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1850000000000001</v>
@@ -1189,13 +1189,13 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-12.3213</v>
+        <v>-10.5093</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.729</v>
+        <v>-9.1309</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5922</v>
+        <v>-1.3784</v>
       </c>
       <c r="G10" t="n">
         <v>-6.912100000000001</v>
@@ -1234,13 +1234,13 @@
         <v>8.3703</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4459</v>
+        <v>1.366</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9313999999999999</v>
+        <v>0.6667000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4854999999999999</v>
+        <v>0.6994</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1173</v>
@@ -1267,13 +1267,13 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-20.9063</v>
+        <v>-17.9692</v>
       </c>
       <c r="E11" t="n">
-        <v>-18.7187</v>
+        <v>-16.7161</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1877</v>
+        <v>-1.2531</v>
       </c>
       <c r="G11" t="n">
         <v>-12.5738</v>
@@ -1312,13 +1312,13 @@
         <v>7.2691</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2558</v>
+        <v>0.6814</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5203</v>
+        <v>0.4824</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7355</v>
+        <v>0.199</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2308</v>
@@ -1345,13 +1345,13 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-25.0027</v>
+        <v>-23.261</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.0502</v>
+        <v>-13.0896</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.9526</v>
+        <v>-10.1714</v>
       </c>
       <c r="G12" t="n">
         <v>-36.115</v>
@@ -1390,13 +1390,13 @@
         <v>50.663</v>
       </c>
       <c r="S12" t="n">
-        <v>6.4906</v>
+        <v>8.232600000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>4.277800000000001</v>
+        <v>5.238600000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>2.2124</v>
+        <v>2.9933</v>
       </c>
       <c r="V12" t="n">
         <v>1.3172</v>
